--- a/pages/shp/uploads/20-11-2025 - 20-11-2025.xlsx
+++ b/pages/shp/uploads/20-11-2025 - 20-11-2025.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="290">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,15 +347,18 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>00026174540620251120000521</t>
-  </si>
-  <si>
-    <t>261</t>
+    <t>00004174540620251120002394</t>
+  </si>
+  <si>
+    <t>41</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -371,10 +374,7 @@
     <t>EXIM MANAGER</t>
   </si>
   <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>026679</t>
+    <t>021516</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -389,111 +389,96 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>258/KM.4/WBC.09/2024</t>
+  </si>
+  <si>
+    <t>12-11-2024 00:00:00</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>PPN</t>
-  </si>
-  <si>
-    <t>PPH</t>
-  </si>
-  <si>
-    <t>BMTP</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289289002007   SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>258/KM.4/WBC.09/2024</t>
-  </si>
-  <si>
-    <t>12-11-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>0739377943422000000000</t>
-  </si>
-  <si>
-    <t>HARMONY TUNAS PRIMA</t>
-  </si>
-  <si>
-    <t>JALAN CIRANGRANG BARAT NO.02 RT.002 RW.001, MARGAHAYU UTARA, BABAKAN CIPARAY, KOTA BANDUNG, JAWA BARAT</t>
+    <t>0030988190027000000000</t>
+  </si>
+  <si>
+    <t>MYUNG SEONG MACHINERY</t>
+  </si>
+  <si>
+    <t>JL RAMIN II DELTA SILICON 6 G 06 NO.18 N RT.000 RW.000, JAYAMUKTI, CIKARANG PUSAT, KABUPATEN BEKASI, JAWA BARAT</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289  SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
-  </si>
-  <si>
     <t>NOMOR DOKUMEN</t>
   </si>
   <si>
@@ -506,84 +491,54 @@
     <t>KODE IJIN</t>
   </si>
   <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>1411/TPB-SK.01/KBC.0903/2025</t>
-  </si>
-  <si>
-    <t>2025-10-02</t>
+    <t>630</t>
+  </si>
+  <si>
+    <t>GEN/OUT/1125/00783</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>085114</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
   </si>
   <si>
     <t>315</t>
   </si>
   <si>
-    <t>160/NAG/KK/X/2025</t>
-  </si>
-  <si>
-    <t>2025-10-01</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>CBD 2025 10 898 01 47694</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>002997/BPJ/CB/2025</t>
-  </si>
-  <si>
-    <t>217</t>
+    <t>MSM/LEASE/202508067</t>
+  </si>
+  <si>
+    <t>KODE CARA ANGKUT</t>
+  </si>
+  <si>
+    <t>NAMA PENGANGKUT</t>
+  </si>
+  <si>
+    <t>NOMOR PENGANGKUT</t>
+  </si>
+  <si>
+    <t>KODE BENDERA</t>
+  </si>
+  <si>
+    <t>CALL SIGN</t>
+  </si>
+  <si>
+    <t>FLAG ANGKUT PLB</t>
+  </si>
+  <si>
+    <t>CARA PENGANGKUTAN LAINNYA</t>
+  </si>
+  <si>
+    <t>MOBIL</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>10/NAG/XI/2025</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>037231</t>
-  </si>
-  <si>
-    <t>2025-09-18</t>
-  </si>
-  <si>
-    <t>KODE CARA ANGKUT</t>
-  </si>
-  <si>
-    <t>NAMA PENGANGKUT</t>
-  </si>
-  <si>
-    <t>NOMOR PENGANGKUT</t>
-  </si>
-  <si>
-    <t>KODE BENDERA</t>
-  </si>
-  <si>
-    <t>CALL SIGN</t>
-  </si>
-  <si>
-    <t>FLAG ANGKUT PLB</t>
-  </si>
-  <si>
-    <t>CARA PENGANGKUTAN LAINNYA</t>
-  </si>
-  <si>
     <t>KODE KEMASAN</t>
   </si>
   <si>
@@ -767,19 +722,16 @@
     <t>STATEMENT PERBEDAAN HARGA</t>
   </si>
   <si>
-    <t>62101019</t>
-  </si>
-  <si>
-    <t>2911</t>
-  </si>
-  <si>
-    <t>PANEL UNTUK DI PRINTING ( COTTON DYED FABRIC 91% COTTON,9% LYCRA )</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>CN</t>
+    <t>84522900</t>
+  </si>
+  <si>
+    <t>29508</t>
+  </si>
+  <si>
+    <t>SEWA MESIN BARTACK MERK TAKATORI, TYPE: TK-430G-01, SN: 201510257, 201510252 / MERK HIKARI, TYPE: HK-430D-A, SN: H04AP00126, H140323018, H131022003 (RETURN)</t>
+  </si>
+  <si>
+    <t>MA</t>
   </si>
   <si>
     <t>T</t>
@@ -842,28 +794,7 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>60062200</t>
-  </si>
-  <si>
-    <t>2896</t>
-  </si>
-  <si>
-    <t>COTTON DYED FABRICS 91% COTTON, 9% LYCRA</t>
-  </si>
-  <si>
-    <t>KGM</t>
-  </si>
-  <si>
-    <t>09-18-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>00002374540620250918000231</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>08-06-2025 00:00:00</t>
   </si>
   <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
@@ -893,15 +824,6 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
-    <t>10-03-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>12-30-2025 00:00:00</t>
-  </si>
-  <si>
     <t>NAMA</t>
   </si>
   <si>
@@ -971,10 +893,16 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>26108</t>
-  </si>
-  <si>
-    <t>026978/KBC.0903/2025</t>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>021521/KBC.0903/2025</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1030,6 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1468,8 +1395,11 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
+      <c r="J2" t="s">
+        <v>107</v>
+      </c>
       <c r="N2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BK2" t="n">
         <v>0.0</v>
@@ -1496,52 +1426,52 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1654887.3</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.0</v>
+        <v>7000000.0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0</v>
+        <v>7000000.0</v>
       </c>
       <c r="CA2" t="n">
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.44</v>
+        <v>200.0</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.32</v>
+        <v>200.0</v>
       </c>
       <c r="CD2" t="n">
         <v>0.0</v>
       </c>
       <c r="CE2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CF2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CG2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="CH2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI2" t="s">
         <v>112</v>
       </c>
       <c r="CP2" t="s">
         <v>113</v>
       </c>
       <c r="CQ2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CT2" t="n">
+        <v>770000.0</v>
+      </c>
+      <c r="CU2" t="n">
         <v>0.0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
@@ -1562,7 +1492,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1573,24 +1503,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -1621,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -1654,13 +1573,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1694,10 +1613,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1709,7 +1628,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1655,7 @@
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="41.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="157.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1746,9 +1665,8 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1770,64 +1688,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1842,52 +1760,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2">
@@ -1901,67 +1819,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="F2" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="G2" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L2" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="M2" t="n">
-        <v>4.32</v>
+        <v>5.0</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="Q2" t="s">
         <v>106</v>
       </c>
       <c r="R2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="S2" t="s">
-        <v>274</v>
-      </c>
-      <c r="T2" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>5554.3</v>
+        <v>0.0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1654887.3</v>
+        <v>0.0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1654887.3</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0</v>
+        <v>7000000.0</v>
       </c>
       <c r="AC2" t="n">
         <v>0.0</v>
@@ -1991,7 +1906,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2022,252 +1937,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G2" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>248233.1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>273</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" t="n">
-        <v>24750.0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>106920.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>273</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>221104.44</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>273</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>50251.01</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>273</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.32</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2301,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2334,7 +2073,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2356,62 +2095,6 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" t="n">
-        <v>221104.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" t="n">
-        <v>50251.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" t="n">
-        <v>106920.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" t="n">
-        <v>248233.0</v>
       </c>
     </row>
   </sheetData>
@@ -2432,16 +2115,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2452,57 +2135,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.79171E8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J2" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2531,13 +2185,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2217,7 @@
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="103.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="112.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2580,49 +2234,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2">
@@ -2630,37 +2284,37 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" t="s">
         <v>138</v>
       </c>
-      <c r="C2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>139</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
         <v>140</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>141</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
         <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3">
@@ -2668,28 +2322,28 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I3" t="s">
         <v>139</v>
       </c>
-      <c r="E3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" t="s">
-        <v>144</v>
-      </c>
       <c r="J3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -2697,28 +2351,28 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I4" t="s">
         <v>139</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>140</v>
-      </c>
-      <c r="F4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" t="s">
-        <v>144</v>
-      </c>
-      <c r="J4" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2741,12 +2395,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -2778,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="D1" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2">
@@ -2792,13 +2446,24 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2821,7 +2486,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="29.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2832,22 +2497,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2">
@@ -2858,13 +2523,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -2875,13 +2540,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -2892,81 +2557,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3002,28 +2599,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
@@ -3033,8 +2630,11 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>138</v>
+      <c r="D2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3065,16 +2665,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -3085,10 +2685,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3121,19 +2721,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3175,61 +2775,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3254,7 +2854,7 @@
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="67.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="157.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3269,7 +2869,6 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3317,58 +2916,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -3380,19 +2979,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -3407,25 +3006,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -3434,94 +3033,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="BK1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
@@ -3532,49 +3131,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="E2" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="K2" t="n">
-        <v>54.0</v>
+        <v>5.0</v>
       </c>
       <c r="L2" t="s">
-        <v>186</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.0</v>
+        <v>171</v>
       </c>
       <c r="T2" t="n">
-        <v>4.32</v>
+        <v>200.0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1654887.3</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1654887.3</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC2" t="n">
         <v>0.0</v>
@@ -3586,7 +3185,7 @@
         <v>0.0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0</v>
+        <v>7000000.0</v>
       </c>
       <c r="AI2" t="n">
         <v>0.0</v>
@@ -3600,17 +3199,11 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>248</v>
-      </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
       <c r="BR2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3656,58 +3249,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
